--- a/XLibur.Tests/Resource/Examples/Misc/Outline.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Outline.xlsx
@@ -364,7 +364,7 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:F5"/>
-  <x:sheetFormatPr defaultRowHeight="15" outlineLevelCol="2"/>
+  <x:sheetFormatPr defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="2"/>
   <x:cols>
     <x:col min="1" max="2" width="9.140625" style="0" customWidth="1"/>
     <x:col min="3" max="4" width="9.140625" style="0" customWidth="1" outlineLevel="2"/>
